--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -244,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>Immunization999999914.Name</t>
+    <t>Immunization999999914.name</t>
   </si>
   <si>
     <t>1</t>
@@ -254,13 +257,13 @@
 </t>
   </si>
   <si>
-    <t>NAME (.01)</t>
-  </si>
-  <si>
-    <t>Immunization999999914.CvxCode</t>
-  </si>
-  <si>
-    <t>CVX CODE (.03)</t>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>Immunization999999914.cvxCode</t>
+  </si>
+  <si>
+    <t>CVX CODE (-.03)</t>
   </si>
 </sst>
 </file>
@@ -491,39 +494,41 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -531,26 +536,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -563,8 +568,8 @@
   <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.8125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.8125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -594,7 +599,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -602,112 +607,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -719,293 +724,295 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,14 +253,24 @@
     <t>1</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>
+  </si>
+  <si>
+    <t>Immunization999999914.cvxCode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element
 </t>
-  </si>
-  <si>
-    <t>NAME (-.01)</t>
-  </si>
-  <si>
-    <t>Immunization999999914.cvxCode</t>
   </si>
   <si>
     <t>CVX CODE (-.03)</t>
@@ -593,7 +603,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -876,13 +886,11 @@
         <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>72</v>
@@ -917,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -943,13 +951,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1000,7 +1008,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>-</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file IMMUNIZATION (9999999.14)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
     <t>NAME (-.01)</t>
   </si>
   <si>
-    <t>example</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file IMMUNIZATION (9999999.14)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source IMMUNIZATION (9999999.14)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,20 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Immunization999999914.cvxCode</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>CVX CODE (-.03)</t>
+  </si>
+  <si>
     <t>Immunization999999914.name</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -264,16 +274,6 @@
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>
-  </si>
-  <si>
-    <t>Immunization999999914.cvxCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
-    <t>CVX CODE (-.03)</t>
   </si>
 </sst>
 </file>
@@ -886,11 +886,13 @@
         <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y3" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z3" t="s" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>72</v>
@@ -925,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -951,13 +953,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -984,13 +986,11 @@
         <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y4" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>72</v>
@@ -1008,7 +1008,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,10 +247,26 @@
     <t>Base</t>
   </si>
   <si>
+    <t>Immunization999999914.name</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>
+  </si>
+  <si>
     <t>Immunization999999914.cvxCode</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Element
@@ -258,22 +274,6 @@
   </si>
   <si>
     <t>CVX CODE (-.03)</t>
-  </si>
-  <si>
-    <t>Immunization999999914.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>NAME (-.01)</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>
   </si>
 </sst>
 </file>
@@ -886,13 +886,11 @@
         <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>72</v>
@@ -927,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -953,13 +951,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -986,11 +984,13 @@
         <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y4" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y4" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z4" t="s" s="2">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>72</v>
@@ -1008,7 +1008,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFinferredCVX-vista</t>
+    <t>http://va.gov/fhir/ValueSet/inferredCVX-vista</t>
   </si>
   <si>
     <t>Immunization999999914.cvxCode</t>
@@ -603,7 +603,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.74609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization999999914.xlsx
+++ b/docs/StructureDefinition-Immunization999999914.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
